--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-14_5_neden_kok_neden_analizi_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-14_5_neden_kok_neden_analizi_formu.xlsx
@@ -961,7 +961,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-14&amp;C&amp;"Arial,Regular"&amp;11 5 Neden Kök Neden Analizi Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Neden sayısı sınırı kaldırıldı; analiz ekseni ve etkinlik kanıtı açıklığa kavuşturuldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>